--- a/p4_modeling/data/England/df_modelos.xlsx
+++ b/p4_modeling/data/England/df_modelos.xlsx
@@ -471,21 +471,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DecisionTreeClassifier(criterion='entropy', max_depth=10, max_features='auto',
-                       min_samples_split=10)</t>
+          <t>DecisionTreeClassifier(criterion='entropy', max_depth=5, max_features='auto',
+                       min_samples_leaf=2, splitter='random')</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>45.92592592592592</v>
+        <v>53.67567567567566</v>
       </c>
       <c r="E2" t="n">
-        <v>56.52173913043478</v>
+        <v>51.45631067961165</v>
       </c>
       <c r="F2" t="n">
-        <v>56.66666666666666</v>
+        <v>44.3984962406015</v>
       </c>
       <c r="G2" t="n">
-        <v>52.42165242165242</v>
+        <v>38.66317169069463</v>
       </c>
     </row>
     <row r="3">
@@ -499,20 +499,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RandomForestClassifier(criterion='entropy', max_depth=3, max_features='auto')</t>
+          <t>RandomForestClassifier(criterion='entropy', max_depth=3, max_features='auto',
+                       min_samples_split=10, n_estimators=500)</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>53.33333333333333</v>
+        <v>55.4054054054054</v>
       </c>
       <c r="E3" t="n">
-        <v>47.82608695652174</v>
+        <v>54.36893203883495</v>
       </c>
       <c r="F3" t="n">
-        <v>43.33333333333334</v>
+        <v>46.1578947368421</v>
       </c>
       <c r="G3" t="n">
-        <v>34.43223443223444</v>
+        <v>39.78643266418239</v>
       </c>
     </row>
     <row r="4">
@@ -528,7 +529,7 @@
         <is>
           <t>XGBClassifier(base_score=None, booster=None, callbacks=None,
               colsample_bylevel=None, colsample_bynode=None,
-              colsample_bytree=0.8, early_stopping_rounds=None,
+              colsample_bytree=1.0, early_stopping_rounds=None,
               enable_categorical=False, eval_metric=None, feature_types=None,
               gamma=None, gpu_id=None, grow_policy=None, importance_type=None,
               interaction_constraints=None, learning_rate=0.01, max_bin=None,
@@ -540,16 +541,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>51.11111111111111</v>
+        <v>55.67567567567568</v>
       </c>
       <c r="E4" t="n">
-        <v>47.82608695652174</v>
+        <v>53.07443365695793</v>
       </c>
       <c r="F4" t="n">
-        <v>43.33333333333334</v>
+        <v>45.48621553884711</v>
       </c>
       <c r="G4" t="n">
-        <v>34.43223443223444</v>
+        <v>39.29907404708466</v>
       </c>
     </row>
     <row r="5">
@@ -563,20 +564,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LogisticRegression(C=0.1, penalty='l1', solver='saga')</t>
+          <t>LogisticRegression(C=0.1, solver='liblinear')</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>53.33333333333333</v>
+        <v>56</v>
       </c>
       <c r="E5" t="n">
-        <v>43.47826086956522</v>
+        <v>53.07443365695793</v>
       </c>
       <c r="F5" t="n">
-        <v>40.83333333333334</v>
+        <v>46.14786967418546</v>
       </c>
       <c r="G5" t="n">
-        <v>41.29013924410344</v>
+        <v>39.74805330937406</v>
       </c>
     </row>
     <row r="6">
@@ -590,20 +591,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SVC(C=5.0, decision_function_shape='ovo')</t>
+          <t>SVC(C=0.1, decision_function_shape='ovo')</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>46.66666666666667</v>
+        <v>55.78378378378378</v>
       </c>
       <c r="E6" t="n">
-        <v>43.47826086956522</v>
+        <v>52.42718446601942</v>
       </c>
       <c r="F6" t="n">
-        <v>43.33333333333334</v>
+        <v>45.15037593984963</v>
       </c>
       <c r="G6" t="n">
-        <v>42.82296650717704</v>
+        <v>38.96528107054422</v>
       </c>
     </row>
     <row r="7">
@@ -617,21 +618,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MLPClassifier(hidden_layer_sizes=(10,), learning_rate='adaptive',
-              learning_rate_init=0.01, solver='sgd')</t>
+          <t>MLPClassifier(alpha=0.01, learning_rate='adaptive', solver='sgd')</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>54.07407407407406</v>
+        <v>55.45945945945946</v>
       </c>
       <c r="E7" t="n">
-        <v>39.1304347826087</v>
+        <v>53.07443365695793</v>
       </c>
       <c r="F7" t="n">
-        <v>33.33333333333333</v>
+        <v>46.54636591478696</v>
       </c>
       <c r="G7" t="n">
-        <v>30.87719298245614</v>
+        <v>41.88905207559328</v>
       </c>
     </row>
     <row r="8">
@@ -645,20 +645,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GradientBoostingClassifier(learning_rate=1)</t>
+          <t>GradientBoostingClassifier(learning_rate=0.01, subsample=0.8)</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>51.11111111111111</v>
+        <v>56.16216216216215</v>
       </c>
       <c r="E8" t="n">
-        <v>47.82608695652174</v>
+        <v>53.72168284789643</v>
       </c>
       <c r="F8" t="n">
-        <v>45.83333333333333</v>
+        <v>45.40852130325814</v>
       </c>
       <c r="G8" t="n">
-        <v>42.23646723646723</v>
+        <v>39.13648455084919</v>
       </c>
     </row>
   </sheetData>
